--- a/MVP-1/ProjectPlan/Development/FlatWire_TrialRunPlan.xlsx
+++ b/MVP-1/ProjectPlan/Development/FlatWire_TrialRunPlan.xlsx
@@ -541,7 +541,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated from the plan of record on August 14, 2026. Never edit this workbook — edit the plan and rebuild.</t>
+          <t>Generated from the plan of record on August 25, 2026. Never edit this workbook — edit the plan and rebuild.</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>This workbook is the trial-run plan the client asked for on 14 August 2026: six operator screens working, with user acceptance testing signed off, by 30 September 2026. It is generated from the plan of record, so every figure in it reconciles to that document rather than being maintained separately.</t>
+          <t>This workbook is the trial-run plan the client asked for on 14 August 2026: six operator screens working, with user acceptance testing signed off. It is generated from the plan of record, so every figure in it reconciles to that document rather than being maintained separately. The request named 30 September 2026. On the staffed team — three resources at six and a half hours a day, starting 31 August — the work completes 3 November and sign-off follows around 16 November. The Sprint Plan sheet shows what a larger team would buy.</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Start at Effort Summary for the shape of the work, then Sprint Plan for the dates and what each staffing option lands. Work Items is the detail — every task with what it delivers. Blockers is what the plan needs from outside the development team. Deferred Items and Removal Impact are the boundary: what is deliberately not in the trial, and what that costs.</t>
+          <t>Start at Effort Summary for the shape of the work, then Sprint Plan for the dates and what a larger team would buy. Work Items is the detail — every task with what it delivers. Blockers is what the plan needs from outside the development team. Deferred Items and Removal Impact are the boundary: what is deliberately not in the trial, and what that costs.</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Effort here is development effort only. Testing, business analysis and contingency are separate and are not included in any figure in this workbook.</t>
+          <t>Effort here is development effort only. Testing, business analysis and contingency are separate and are not included in any figure in this workbook. A day in this workbook is a six-and-a-half-hour day, being the time each resource commits to this project rather than the length of their working day; the hours themselves are unchanged.</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1121,7 +1121,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Where the 832 hours of development effort sit, by block of work and by discipline. Development only — testing, business analysis and contingency are separate and are not included.</t>
+          <t>Where the 869 hours of development effort sit, by block of work and by discipline. Development only — testing, business analysis and contingency are separate and are not included.</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Days</t>
+          <t>Days (6.5 h)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1154,14 +1154,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>57.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>56 %</t>
+          <t>55 %</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>74</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>89</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>11.1</v>
+        <v>13.7</v>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>67</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>8.4</v>
+        <v>10.3</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>38</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
@@ -1292,144 +1292,162 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Flattening Lines 2 and 3 run-end write-back (FW-219)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>5 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
-        <v>832</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>104</v>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="B14" s="10" t="n">
+        <v>869</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>100 %</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>The platform is the largest single block and has not been started. Reducing screen scope is the weakest lever available to this plan; shortening the platform is the strongest.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>By discipline</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Discipline</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Days</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Days (6.5 h)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Frontend (Angular)</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B20" s="7" t="n">
         <v>329</v>
       </c>
-      <c r="C19" s="7" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>40 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="C20" s="7" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>38 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Backend (.NET)</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="n">
+        <v>264</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>30 %</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Real-time and controller integration</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B22" s="7" t="n">
         <v>141</v>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>17 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="C22" s="7" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>16 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Database (SQL Server)</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>13 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="B23" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>16 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
-        <v>832</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>104</v>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="B24" s="10" t="n">
+        <v>869</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>100 %</t>
         </is>
@@ -1447,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1456,7 +1474,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1507,7 +1525,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Days</t>
+          <t>Days (6.5 h)</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1534,7 +1552,7 @@
         <v>166</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>20.8</v>
+        <v>25.5</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
@@ -1560,7 +1578,7 @@
         <v>231</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>28.9</v>
+        <v>35.5</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
@@ -1577,14 +1595,14 @@
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="7" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>8.1</v>
+        <v>9.5</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
@@ -1610,7 +1628,7 @@
         <v>15</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
@@ -1640,7 +1658,7 @@
         <v>74</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>9.199999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -1668,7 +1686,7 @@
         <v>89</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>11.1</v>
+        <v>13.7</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
@@ -1698,7 +1716,7 @@
         <v>56</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -1728,7 +1746,7 @@
         <v>31</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
@@ -1758,7 +1776,7 @@
         <v>67</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>8.4</v>
+        <v>10.3</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -1788,7 +1806,7 @@
         <v>38</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
@@ -1797,47 +1815,73 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>FW-219 run-end write-back</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B16" s="10" t="n">
         <v>329</v>
       </c>
-      <c r="C15" s="10" t="n">
-        <v>250</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>112</v>
-      </c>
-      <c r="E15" s="10" t="n">
+      <c r="C16" s="10" t="n">
+        <v>264</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="E16" s="10" t="n">
         <v>141</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>832</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>104</v>
-      </c>
-      <c r="H15" s="10" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>The platform is three unequal problems that genuinely run in parallel, which is why an extra person pays for itself in the first sprint and nowhere else.</t>
-        </is>
-      </c>
+      <c r="F16" s="10" t="n">
+        <v>869</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="H16" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Real-time and controller integration is concentrated in the platform: after it, only 39 hours remain across five blocks, so that owner picks up database or service work.</t>
+          <t>The platform is three unequal problems that genuinely run in parallel, which is why an extra person pays for itself in the first sprint and nowhere else.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Real-time and controller integration is concentrated in the platform: after it, only 39 hours remain across five blocks, so that owner picks up database or service work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Spool completion is the only block that is service-heavy, and it is also last and gates the finishing line — so that owner holds the end of the schedule.</t>
         </is>
@@ -1877,7 +1921,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>462 hours, 54 per cent of the trial, not yet started. Broken out to deliverable level because a single figure for the platform is not something anyone can act on.</t>
+          <t>459 hours, 54 per cent of the trial, not yet started. Broken out to deliverable level because a single figure for the platform is not something anyone can act on.</t>
         </is>
       </c>
     </row>
@@ -1977,21 +2021,21 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>−36</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G7" s="7" t="n"/>
     </row>
@@ -2002,21 +2046,21 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>1110</v>
+        <v>1027</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>535</v>
+        <v>496</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>−73 h</t>
+          <t>−37 h</t>
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>53</v>
@@ -2115,16 +2159,16 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
@@ -2134,16 +2178,16 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="20">
@@ -2807,7 +2851,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>⚠ Shared-schema renames + new columns (16 rename + 40 impact audit)</t>
+          <t>⚠ Shared-schema renames + new columns — CANCELLED, D-32 (was 16 rename + 40 impact audit)</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -2815,9 +2859,7 @@
           <t>FW-001</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
-        <v>56</v>
-      </c>
+      <c r="C62" s="7" t="n"/>
       <c r="D62" s="7" t="n">
         <v>0</v>
       </c>
@@ -2825,7 +2867,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>INFLAT coil status</t>
+          <t>INFLAT coil status — CANCELLED, D-32 (was 4 h)</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -2833,11 +2875,9 @@
           <t>FW-002</t>
         </is>
       </c>
-      <c r="C63" s="8" t="n">
-        <v>4</v>
-      </c>
+      <c r="C63" s="8" t="n"/>
       <c r="D63" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -2939,7 +2979,7 @@
       <c r="B69" s="10" t="inlineStr"/>
       <c r="C69" s="10" t="n"/>
       <c r="D69" s="10" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2964,7 +3004,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -3019,7 +3059,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Days</t>
+          <t>Days (6.5 h)</t>
         </is>
       </c>
     </row>
@@ -3051,14 +3091,14 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
         <v>14</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="6">
@@ -3089,14 +3129,14 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
         <v>11</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="7">
@@ -3127,14 +3167,14 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
         <v>8</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
@@ -3165,14 +3205,14 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G8" s="8" t="n">
         <v>14</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -3203,14 +3243,14 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
         <v>16</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -3241,14 +3281,14 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
         <v>8</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -3279,14 +3319,14 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
         <v>8</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
@@ -3317,14 +3357,14 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
         <v>11</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -3355,14 +3395,14 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14">
@@ -3393,14 +3433,14 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="15">
@@ -3431,14 +3471,14 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16">
@@ -3469,14 +3509,14 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
         <v>21</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -3507,14 +3547,14 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18">
@@ -3545,35 +3585,35 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G18" s="8" t="n">
         <v>11</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>FW-002</t>
+          <t>FW-004</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Being-flattened material status</t>
+          <t>Alloy reference data</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>A rod that is being flattened shows that state everywhere in the business, not only inside the new module.</t>
+          <t>Alloy properties are data the business can maintain, not values built into the code.</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>INFLAT coil status</t>
+          <t>AlloyProperty lookup and seed</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -3583,35 +3623,35 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>FW-004</t>
+          <t>FW-005</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Alloy reference data</t>
+          <t>Equipment reference data</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Alloy properties are data the business can maintain, not values built into the code.</t>
+          <t>The fixed reference data every screen reads — mill stands, drawing dies, edgers, spool configurations and payoff positions — exists and is populated.</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AlloyProperty lookup and seed</t>
+          <t>Lookup group tables and seed</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -3621,35 +3661,35 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G20" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>FW-005</t>
+          <t>FW-006</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Equipment reference data</t>
+          <t>Material records</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>The fixed reference data every screen reads — mill stands, drawing dies, edgers, spool configurations and payoff positions — exists and is populated.</t>
+          <t>Rods, spools and production runs have somewhere to be recorded.</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Lookup group tables and seed</t>
+          <t>Materials group tables</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -3659,11 +3699,11 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>1.2</v>
@@ -3672,22 +3712,22 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>FW-006</t>
+          <t>FW-007</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Material records</t>
+          <t>Run and quality records</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Rods, spools and production runs have somewhere to be recorded.</t>
+          <t>Every event an operator records during a run — check-ins, quality checkpoints, pauses, adjustments, rejections and output — has a place to be stored against its run and the footage it happened at.</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Materials group tables</t>
+          <t>Runs and Quality/Output group tables</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3697,35 +3737,35 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G22" s="8" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>FW-007</t>
+          <t>FW-152</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Run and quality records</t>
+          <t>Database build and rebuild</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Every event an operator records during a run — check-ins, quality checkpoints, pauses, adjustments, rejections and output — has a place to be stored against its run and the footage it happened at.</t>
+          <t>The database is built from scripts in a known order and can be rebuilt identically at any time, which is what makes a repeatable test environment possible.</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Runs and Quality/Output group tables</t>
+          <t>FlatWireDB creation, ordered database build script runner, indexes and grants</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -3735,73 +3775,73 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>FW-152</t>
+          <t>FW-130</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Database build and rebuild</t>
+          <t>Shopfloor screen layout</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>The database is built from scripts in a known order and can be rebuilt identically at any time, which is what makes a repeatable test environment possible.</t>
+          <t>Every screen is laid out for the panel size it will actually run on, so nothing has to be re-fitted after it is built.</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>FlatWireDB creation, ordered database build script runner, indexes and grants</t>
+          <t>Shell layout and the 1280×1024 shopfloor canvas</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Database (SQL Server)</t>
+          <t>Frontend (Angular)</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G24" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>FW-130</t>
+          <t>FW-131</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Shopfloor screen layout</t>
+          <t>Access control and error handling</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Every screen is laid out for the panel size it will actually run on, so nothing has to be re-fitted after it is built.</t>
+          <t>A signed-out or unauthorised user cannot reach an operator screen, and a failed request shows one readable message instead of a blank panel.</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Shell layout and the 1280×1024 shopfloor canvas</t>
+          <t>Route guards, interceptor wiring and the error envelope</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -3811,35 +3851,35 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G25" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>FW-131</t>
+          <t>FW-132</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Access control and error handling</t>
+          <t>Data access layer for the screens</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>A signed-out or unauthorised user cannot reach an operator screen, and a failed request shows one readable message instead of a blank panel.</t>
+          <t>Screens can be built and demonstrated against sample data before the services behind them exist, which is what allows screen and service work to run in parallel.</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Route guards, interceptor wiring and the error envelope</t>
+          <t>Dependency-injection-swappable API client and domain models</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3849,35 +3889,35 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G26" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>FW-132</t>
+          <t>FW-133</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Data access layer for the screens</t>
+          <t>The six shared screen controls</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Screens can be built and demonstrated against sample data before the services behind them exist, which is what allows screen and service work to run in parallel.</t>
+          <t>The six controls that appear across the whole application, built once: the pass schedule table and its confirmation bar, the quality trace chart, the guided step wizard, the action bar and the material weight bar. Every one of the six trial screens depends on all six, which is why nothing downstream starts until this is done.</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Dependency-injection-swappable API client and domain models</t>
+          <t>Shared composite controls</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -3887,35 +3927,35 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G27" s="7" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>FW-133</t>
+          <t>FW-134</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>The six shared screen controls</t>
+          <t>Shared inputs, readouts and warnings</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>The six controls that appear across the whole application, built once: the pass schedule table and its confirmation bar, the quality trace chart, the guided step wizard, the action bar and the material weight bar. Every one of the six trial screens depends on all six, which is why nothing downstream starts until this is done.</t>
+          <t>Consistent entry fields, measurement readouts, pass and fail buttons and warning banners across every screen, so the application reads as one system rather than a set of pages.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Shared composite controls</t>
+          <t>Shared primitive controls and alert-banner</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3925,35 +3965,35 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G28" s="8" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>FW-134</t>
+          <t>FW-N03</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Shared inputs, readouts and warnings</t>
+          <t>Operator application created</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Consistent entry fields, measurement readouts, pass and fail buttons and warning banners across every screen, so the application reads as one system rather than a set of pages.</t>
+          <t>The operator application exists as something the team can build, run and deploy, with its screens routed and its settings in place.</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Shared primitive controls and alert-banner</t>
+          <t>Angular library scaffold, routing and configuration</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -3963,73 +4003,73 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G29" s="7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>FW-N03</t>
+          <t>FW-080</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Operator application created</t>
+          <t>Live data broadcast channel</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>The operator application exists as something the team can build, run and deploy, with its screens routed and its settings in place.</t>
+          <t>The channel that pushes live readings to every connected screen, separated by line so a screen only receives the line it is showing.</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Angular library scaffold, routing and configuration</t>
+          <t>FlatWireHub — strongly-typed, MessagePack, line groups</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Frontend (Angular)</t>
+          <t>Real-time and controller integration</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G30" s="8" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>FW-080</t>
+          <t>FW-135</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Live data broadcast channel</t>
+          <t>Live connection in the screens</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>The channel that pushes live readings to every connected screen, separated by line so a screen only receives the line it is showing.</t>
+          <t>The screens hold an open connection and receive readings as they happen, rather than refreshing to look for them.</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>FlatWireHub — strongly-typed, MessagePack, line groups</t>
+          <t>SignalR client service</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -4039,35 +4079,35 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G31" s="7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>FW-135</t>
+          <t>FW-136</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Live connection in the screens</t>
+          <t>Simulated live feed for the screens</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>The screens hold an open connection and receive readings as they happen, rather than refreshing to look for them.</t>
+          <t>A stand-in live feed so every moving screen can be built and reviewed before anything is connected to the plant. Small, and the single most valuable piece of schedule insurance in the plan.</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>SignalR client service</t>
+          <t>MockSignalRService and the typed event set</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -4077,35 +4117,35 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G32" s="8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>FW-136</t>
+          <t>FW-137</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Simulated live feed for the screens</t>
+          <t>Offline resilience</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>A stand-in live feed so every moving screen can be built and reviewed before anything is connected to the plant. Small, and the single most valuable piece of schedule insurance in the plan.</t>
+          <t>A dropped network shows a clear banner over the last known readings instead of an empty screen, and the connection recovers by itself.</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>MockSignalRService and the typed event set</t>
+          <t>Offline cache sync and the reconnect banner</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -4115,35 +4155,35 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G33" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>FW-137</t>
+          <t>FW-149</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Offline resilience</t>
+          <t>Live message definitions</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>A dropped network shows a clear banner over the last known readings instead of an empty screen, and the connection recovers by itself.</t>
+          <t>One agreed definition of every live message, so the screens and the service cannot drift apart on what a reading contains.</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Offline cache sync and the reconnect banner</t>
+          <t>IFlatWireClient typed event contract</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -4153,73 +4193,73 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="G34" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>FW-149</t>
+          <t>FW-150</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Live message definitions</t>
+          <t>Live reading delivery</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>One agreed definition of every live message, so the screens and the service cannot drift apart on what a reading contains.</t>
+          <t>Readings are grouped and sent at a steady rate, so a high-frequency measurement feed reaches the screens without overwhelming them.</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>IFlatWireClient typed event contract</t>
+          <t>Cadence-driven broadcast loop</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Real-time and controller integration</t>
+          <t>Backend foundation close-out</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G35" s="7" t="n">
         <v>11</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>FW-150</t>
+          <t>FW-151</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Live reading delivery</t>
+          <t>Machine settings service, with simulation</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Readings are grouped and sent at a steady rate, so a high-frequency measurement feed reaches the screens without overwhelming them.</t>
+          <t>Machine settings can be written from the application, and simulated instead when no machine is connected. Every check-in stage can therefore be built and demonstrated long before commissioning.</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Cadence-driven broadcast loop</t>
+          <t>PLCTagService skeleton and SimulatePLCTagPush</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -4229,35 +4269,35 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G36" s="8" t="n">
         <v>11</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>FW-151</t>
+          <t>FW-203</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Machine settings service, with simulation</t>
+          <t>Simulated machine data feed</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Machine settings can be written from the application, and simulated instead when no machine is connected. Every check-in stage can therefore be built and demonstrated long before commissioning.</t>
+          <t>Realistic live readings without a machine, and steerable — an in-tolerance run, a drifting one, an out-of-tolerance excursion or a line stop can each be reproduced on demand, so the screens are accepted against known conditions rather than whatever the plant happens to be doing.</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>PLCTagService skeleton and SimulatePLCTagPush</t>
+          <t>Plant data feed simulator — a stand-in for the real ingest</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -4267,35 +4307,35 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G37" s="7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>FW-203</t>
+          <t>FW-205</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Simulated machine data feed</t>
+          <t>Run-block interlock</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Realistic live readings without a machine, and steerable — an in-tolerance run, a drifting one, an out-of-tolerance excursion or a line stop can each be reproduced on demand, so the screens are accepted against known conditions rather than whatever the plant happens to be doing.</t>
+          <t>The line is prevented from running whenever the system cannot account for what it is producing — no material checked in, or the footage feed missing or invalid. It clears by itself when the cause clears, and it blocks one line without affecting the others.</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Plant data feed simulator — a stand-in for the real ingest</t>
+          <t>ITInhibitService — the run-block interlock</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -4305,35 +4345,35 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G38" s="8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>FW-205</t>
+          <t>FW-218</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Run-block interlock</t>
+          <t>Controls for the simulated machine data feed</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>The line is prevented from running whenever the system cannot account for what it is producing — no material checked in, or the footage feed missing or invalid. It clears by itself when the cause clears, and it blocks one line without affecting the others.</t>
+          <t>A way to drive the simulated line while a run is in progress, so the acceptance run can be performed at all. Three of its ten steps depend on it: pushing a run out of tolerance to prove the automatic quality prompt fires, stopping the line at a chosen instant to prove the spool completion prompt behaves correctly on a brief stop, and interrupting the data feed to prove the machine is blocked when readings go missing. Restarting the feed with different settings cannot do any of this — it ends the run being demonstrated. The controls are for engineers, are never available to an operator, and do not exist at all once the system is connected to a real machine.</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>ITInhibitService — the run-block interlock</t>
+          <t>Trial control surface for the feed generator — steer, stop, drop, read</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -4343,73 +4383,73 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>FW-218</t>
+          <t>FW-061</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Controls for the simulated machine data feed</t>
+          <t>Rod check-in screen</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>A way to drive the simulated line while a run is in progress, so the acceptance run can be performed at all. Three of its ten steps depend on it: pushing a run out of tolerance to prove the automatic quality prompt fires, stopping the line at a chosen instant to prove the spool completion prompt behaves correctly on a brief stop, and interrupting the data feed to prove the machine is blocked when readings go missing. Restarting the feed with different settings cannot do any of this — it ends the run being demonstrated. The controls are for engineers, are never available to an operator, and do not exist at all once the system is connected to a real machine.</t>
+          <t>The rod check-in screen — a guided six-step sequence that will not let a run start until the material, the inspection, the measurements and the mill schedule have each been confirmed.</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Trial control surface for the feed generator — steer, stop, drop, read</t>
+          <t>Dashboard 2 — Rod Check-in six-step wizard (Flattening Line 1/Flattening Line 3 (hybrid))</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>Backend foundation close-out</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G40" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>FW-061</t>
+          <t>FW-082</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Rod check-in screen</t>
+          <t>Machine configuration on check-in</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>The rod check-in screen — a guided six-step sequence that will not let a run start until the material, the inspection, the measurements and the mill schedule have each been confirmed.</t>
+          <t>Acknowledging the schedule is what configures the mill — die sizes, roll gaps, edge type, speed limits and dimensional targets. The machine is never set from a schedule nobody confirmed.</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Dashboard 2 — Rod Check-in six-step wizard (Flattening Line 1/Flattening Line 3 (hybrid))</t>
+          <t>Programmable Logic Controller tag group push on check-in acknowledgement</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4419,35 +4459,35 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G41" s="7" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>FW-082</t>
+          <t>FW-157</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Machine configuration on check-in</t>
+          <t>Rod check-in transaction</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Acknowledging the schedule is what configures the mill — die sizes, roll gaps, edge type, speed limits and dimensional targets. The machine is never set from a schedule nobody confirmed.</t>
+          <t>Checking in a rod records the inspection, the measurements and the run before anything is sent to the machine, and marks the rod as being flattened across the business.</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Programmable Logic Controller tag group push on check-in acknowledgement</t>
+          <t>POST /checkin/rod and CheckInService</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -4457,35 +4497,35 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G42" s="8" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>FW-157</t>
+          <t>FW-159</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Rod check-in transaction</t>
+          <t>Check-in write sequence</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Checking in a rod records the inspection, the measurements and the run before anything is sent to the machine, and marks the rod as being flattened across the business.</t>
+          <t>The check-in writes land in the correct order across two databases, so a failure part-way through cannot leave one rod recorded in two different states.</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>POST /checkin/rod and CheckInService</t>
+          <t>RodStaging, the check-in write path and the INFLAT write</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4495,73 +4535,73 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G43" s="7" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>FW-159</t>
+          <t>FW-062</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Check-in write sequence</t>
+          <t>Active run monitor</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>The check-in writes land in the correct order across two databases, so a failure part-way through cannot leave one rod recorded in two different states.</t>
+          <t>The screen an operator watches for the whole run: live thickness and width against tolerance, machine and material state, and one-touch access to every action that can be taken without stopping.</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>RodStaging, the check-in write path and the cross-database INFLAT write</t>
+          <t>Dashboard 3 — Active Run Monitor (Flattening Line 1) and Flattening Line 3 (hybrid) variant</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G44" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>FW-062</t>
+          <t>FW-081</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Active run monitor</t>
+          <t>Live quality trace chart</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>The screen an operator watches for the whole run: live thickness and width against tolerance, machine and material state, and one-touch access to every action that can be taken without stopping.</t>
+          <t>The live quality trace with its target and tolerance band drawn on it, expandable to fill the screen, and able to switch between live readings and a completed run's recorded history.</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Dashboard 3 — Active Run Monitor (Flattening Line 1) and Flattening Line 3 (hybrid) variant</t>
+          <t>gauge-trace-chart live streaming, maximize and runtime source toggle</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4571,35 +4611,35 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G45" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>FW-081</t>
+          <t>FW-162</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Live quality trace chart</t>
+          <t>Run status cards</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>The live quality trace with its target and tolerance band drawn on it, expandable to fill the screen, and able to switch between live readings and a completed run's recorded history.</t>
+          <t>Machine state, material flow and mill configuration readable at a glance from across the aisle.</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>gauge-trace-chart live streaming, maximize and runtime source toggle</t>
+          <t>run-status-cards</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -4609,35 +4649,35 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G46" s="8" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>FW-162</t>
+          <t>FW-163</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Run status cards</t>
+          <t>Order and material detail panels</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Machine state, material flow and mill configuration readable at a glance from across the aisle.</t>
+          <t>Order and material detail available on the run screen without leaving it, and collapsible so it never crowds the quality trace.</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>run-status-cards</t>
+          <t>info-grid and chart-tab-strip</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4647,35 +4687,35 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G47" s="7" t="n">
         <v>13</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>FW-163</t>
+          <t>FW-164</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Order and material detail panels</t>
+          <t>Run lookup and history</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Order and material detail available on the run screen without leaving it, and collapsible so it never crowds the quality trace.</t>
+          <t>A screen can pick a run back up after a refresh or a shift change, and read a finished run's quality history.</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>info-grid and chart-tab-strip</t>
+          <t>GET /run/active, GET /run/{runId}/gaugetrace and RunQueryService</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -4685,35 +4725,35 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G48" s="8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>FW-164</t>
+          <t>FW-165</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Run lookup and history</t>
+          <t>Fast quality history retrieval</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>A screen can pick a run back up after a refresh or a shift change, and read a finished run's quality history.</t>
+          <t>A long run's quality history loads quickly instead of pulling back every individual reading.</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>GET /run/active, GET /run/{runId}/gaugetrace and RunQueryService</t>
+          <t>sp_GetGaugeTrace</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4723,35 +4763,35 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G49" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>FW-165</t>
+          <t>FW-214</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Fast quality history retrieval</t>
+          <t>Engineering console for the simulated machine</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>A long run's quality history loads quickly instead of pulling back every individual reading.</t>
+          <t>One screen an engineer drives all three simulated lines from, so the acceptance run is a few clicks rather than typed commands with a stopwatch — which matters because the run is performed in front of the client and one of its checks is a three-second stop measured against a five-second threshold. It is an engineering tool, not an operator screen: it is absent from the dashboard inventory and the navigation, and it does not exist at all once the system is connected to a real machine. Several of its controls arrive switched off, because the behaviour behind them is deliberately not being built for the trial.</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>sp_GetGaugeTrace</t>
+          <t>Simulator control console — screen Database (SQL Server)-sprint one</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -4761,73 +4801,73 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G50" s="8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>FW-214</t>
+          <t>FW-065</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Engineering console for the simulated machine</t>
+          <t>Quality checkpoint capture</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>One screen an engineer drives all three simulated lines from, so the acceptance run is a few clicks rather than typed commands with a stopwatch — which matters because the run is performed in front of the client and one of its checks is a three-second stop measured against a five-second threshold. It is an engineering tool, not an operator screen: it is absent from the dashboard inventory and the navigation, and it does not exist at all once the system is connected to a real machine. Several of its controls arrive switched off, because the behaviour behind them is deliberately not being built for the trial.</t>
+          <t>Recording a quality checkpoint without leaving the running screen, with the measurement shown against its tolerance, and a direct route to holding the material when it is outside specification.</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Simulator control console — screen Database (SQL Server)-sprint one</t>
+          <t>Statistical Process Control checkpoint dialog</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6 (start)</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G51" s="7" t="n">
         <v>15</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>FW-065</t>
+          <t>FW-071</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Quality checkpoint capture</t>
+          <t>Pause and resume capture</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Recording a quality checkpoint without leaving the running screen, with the measurement shown against its tolerance, and a direct route to holding the material when it is outside specification.</t>
+          <t>Downtime is captured with a reason the business can report on, footage is frozen at the moment of the pause, and resuming offers the operator only the outcomes that make sense at that point.</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Statistical Process Control checkpoint dialog</t>
+          <t>Pause and Resume dialogs</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -4837,35 +4877,35 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G52" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>FW-071</t>
+          <t>FW-168</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Pause and resume capture</t>
+          <t>Quality checkpoint transaction</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Downtime is captured with a reason the business can report on, footage is frozen at the moment of the pause, and resuming offers the operator only the outcomes that make sense at that point.</t>
+          <t>Checkpoint measurements are stored against the run and the footage they were taken at, and a result outside specification puts the material on hold.</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Pause and Resume dialogs</t>
+          <t>POST /spc and SpcService</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -4875,35 +4915,35 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G53" s="7" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>FW-168</t>
+          <t>FW-170</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Quality checkpoint transaction</t>
+          <t>Pause and resume transaction</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Checkpoint measurements are stored against the run and the footage they were taken at, and a result outside specification puts the material on hold.</t>
+          <t>Pausing and resuming is recorded with its duration, and the machine is idled and restored along with it.</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>POST /spc and SpcService</t>
+          <t>POST /run/{id}/pause and /resume, and RunControlService</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -4913,35 +4953,35 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G54" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>FW-170</t>
+          <t>FW-171</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Pause and resume transaction</t>
+          <t>In-run event records</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Pausing and resuming is recorded with its duration, and the machine is idled and restored along with it.</t>
+          <t>Quality checkpoints, their measurements and pause events have somewhere to be recorded against their run.</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>POST /run/{id}/pause and /resume, and RunControlService</t>
+          <t>The five in-run event tables</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -4951,73 +4991,73 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G55" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>FW-171</t>
+          <t>FW-153</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>In-run event records</t>
+          <t>Connection loss handling</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Quality checkpoints, their measurements and pause events have somewhere to be recorded against their run.</t>
+          <t>A network drop never shows an operator a blank screen. The last known state stays visible with a clear warning until the connection returns.</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>The five in-run event tables</t>
+          <t>Alert chips, reconnect banner and cached-state fallback</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>6 (start)</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G56" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>FW-153</t>
+          <t>FW-155</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Connection loss handling</t>
+          <t>Fast active-run lookup</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>A network drop never shows an operator a blank screen. The last known state stays visible with a clear warning until the connection returns.</t>
+          <t>Finding a line's current run stays instant as years of run history accumulate.</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Alert chips, reconnect banner and cached-state fallback</t>
+          <t>FlatWireRun(LineId, Status) index</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5027,35 +5067,35 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G57" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>FW-155</t>
+          <t>FW-204</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Fast active-run lookup</t>
+          <t>Line picker entry screen</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Finding a line's current run stays instant as years of run history accumulate.</t>
+          <t>An operator arriving at a terminal picks their line and lands on the right screen for whatever that line is doing. It is retired when the full line status board ships.</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>FlatWireRun(LineId, Status) index</t>
+          <t>Minimal landing route — the entry point when Dashboard 1 is out of scope</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -5065,111 +5105,111 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="G58" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>FW-204</t>
+          <t>FW-172</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Line picker entry screen</t>
+          <t>Events marked on the quality trace</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>An operator arriving at a terminal picks their line and lands on the right screen for whatever that line is doing. It is retired when the full line status board ships.</t>
+          <t>Actions an operator takes appear on the run's quality trace at the footage where they happened, so anyone reviewing the run afterwards can see what was done and when.</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Minimal landing route — the entry point when Dashboard 1 is out of scope</t>
+          <t>Run-event markers and the LineStatus transitions</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>navigation</t>
+          <t>6 close</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G59" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>FW-172</t>
+          <t>FW-067</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Events marked on the quality trace</t>
+          <t>Material rejection capture</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Actions an operator takes appear on the run's quality trace at the footage where they happened, so anyone reviewing the run afterwards can see what was done and when.</t>
+          <t>Suspect material is taken out of production with a reason, a decision on what happens to it and a permanent record — raised from wherever the operator noticed the problem.</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Run-event markers and the LineStatus transitions</t>
+          <t>Work-in-Progress rejection dialog</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>6 close</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G60" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>FW-067</t>
+          <t>FW-174</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Material rejection capture</t>
+          <t>Rejection transaction</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Suspect material is taken out of production with a reason, a decision on what happens to it and a permanent record — raised from wherever the operator noticed the problem.</t>
+          <t>A rejection sets the material's status, files it in the held queue and raises an alert to a supervisor.</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Work-in-Progress rejection dialog</t>
+          <t>POST /wipreject, POST /checkout and their services</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5179,35 +5219,35 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G61" s="7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>FW-174</t>
+          <t>FW-176</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Rejection transaction</t>
+          <t>Rejection records</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>A rejection sets the material's status, files it in the held queue and raises an alert to a supervisor.</t>
+          <t>Rejections and the decision taken on each have somewhere to be recorded.</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>POST /wipreject, POST /checkout and their services</t>
+          <t>WipRejection / RodCheckout tables and the shared coils carry-forward columns</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -5217,35 +5257,35 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G62" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>FW-176</t>
+          <t>FW-177</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Rejection records</t>
+          <t>Supervisor notification</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Rejections and the decision taken on each have somewhere to be recorded.</t>
+          <t>A supervisor is told when material is held, rather than discovering it at the end of the shift.</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>WipRejection / RodCheckout tables and the shared coils carry-forward columns</t>
+          <t>Exception broadcasts and the supervisor notification</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -5255,73 +5295,73 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G63" s="7" t="n">
         <v>5</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>FW-177</t>
+          <t>FW-064</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Supervisor notification</t>
+          <t>Spool check-in screen</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>A supervisor is told when material is held, rather than discovering it at the end of the shift.</t>
+          <t>The finishing line's check-in screen: the arriving spool's quality history and the material it came from, shown before anything is committed, with the mill configuration confirmed separately.</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Exception broadcasts and the supervisor notification</t>
+          <t>Dashboard 5 — Flattening Line 2 Spool Check-in</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G64" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>FW-064</t>
+          <t>FW-178</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Spool check-in screen</t>
+          <t>Run monitor for the finishing line</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>The finishing line's check-in screen: the arriving spool's quality history and the material it came from, shown before anything is committed, with the mill configuration confirmed separately.</t>
+          <t>The same run monitor configured for the finishing line, showing one spool draining and one coil filling rather than two rod payoffs.</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Dashboard 5 — Flattening Line 2 Spool Check-in</t>
+          <t>Dashboard 3 Flattening Line 2 variant configuration</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -5331,35 +5371,35 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G65" s="7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>FW-178</t>
+          <t>FW-179</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Run monitor for the finishing line</t>
+          <t>Spool check-in transaction</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>The same run monitor configured for the finishing line, showing one spool draining and one coil filling rather than two rod payoffs.</t>
+          <t>Checking in a spool configures the finishing mill and starts its run, and the operator can see what material is waiting to be processed.</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Dashboard 3 Flattening Line 2 variant configuration</t>
+          <t>POST /checkin/spool and GET /spools</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -5369,35 +5409,35 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G66" s="8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>FW-179</t>
+          <t>FW-180</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Spool check-in transaction</t>
+          <t>Spool check-in records</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Checking in a spool configures the finishing mill and starts its run, and the operator can see what material is waiting to be processed.</t>
+          <t>Finishing-line check-ins have somewhere to be recorded, and finding a spool by its order stays fast.</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>POST /checkin/spool and GET /spools</t>
+          <t>SpoolCheckin table and the SpoolProcessing.OrderNo index</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -5407,35 +5447,35 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G67" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>FW-180</t>
+          <t>FW-181</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Spool check-in records</t>
+          <t>Honest live reading on the finishing line</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Finishing-line check-ins have somewhere to be recorded, and finding a spool by its order stays fast.</t>
+          <t>The finishing line states plainly that it has no live thickness measurement, instead of drawing a flat line at target that an operator would reasonably read as a real in-tolerance measurement.</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>SpoolCheckin table and the Spool.OrderNo index</t>
+          <t>Flattening Line 2 null-gauge contract and the Live/Profile binding</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -5445,73 +5485,73 @@
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G68" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>FW-181</t>
+          <t>FW-202</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Honest live reading on the finishing line</t>
+          <t>Spool completion and weighing</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>The finishing line states plainly that it has no live thickness measurement, instead of drawing a flat line at target that an operator would reasonably read as a real in-tolerance measurement.</t>
+          <t>The transaction that turns a finished run into a real, weighed, traceable spool. The machine stop is confirmed with the weight held at the moment it stopped, the operator can enter a scale weight instead and is warned if the two disagree, and the spool record is created with its source material and footage. Nothing else in the trial creates the spool that the finishing line checks in.</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Flattening Line 2 null-gauge contract and the Live/Profile binding</t>
+          <t>Flattening Line 1 spool completion — stop confirmation, weight basis and the SpoolProcessing write</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>new</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G69" s="7" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0.4</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>FW-202</t>
+          <t>FW-219</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Spool completion and weighing</t>
+          <t>Finished coil recorded plant-wide</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>The transaction that turns a finished run into a real, weighed, traceable spool. The machine stop is confirmed with the weight held at the moment it stopped, the operator can enter a scale weight instead and is warned if the two disagree, and the spool record is created with its source material and footage. Nothing else in the trial creates the spool that the finishing line checks in.</t>
+          <t>A finished coil that the rest of the plant can actually see. Completing a coil currently records it in the flat wire system alone, so packing cannot find it, shipping cannot ship it, certification has no chain back to the rod, and it never reaches cost or yield reporting. This creates the same set of records any other finished coil at United Aluminum has — the coil itself, its link to the order, its genealogy back to the source rod, its cost record, its skid and its shop-floor transaction — either all together or not at all, so the coil is never complete on one system and missing from the others. It also settles where a flat wire skid is recorded: in the existing shop-floor skid register, numbered by the existing rule, with no new table built.</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Flattening Line 1 spool completion — stop confirmation, weight basis and the Spool write</t>
+          <t>Flattening Lines 2 and 3 run-end write-back into the shared schema</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -5521,14 +5561,14 @@
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="G70" s="8" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="71">
@@ -5543,10 +5583,10 @@
       <c r="E71" s="9" t="inlineStr"/>
       <c r="F71" s="10" t="inlineStr"/>
       <c r="G71" s="10" t="n">
-        <v>832</v>
+        <v>869</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>104</v>
+        <v>133.7</v>
       </c>
     </row>
   </sheetData>
@@ -5585,7 +5625,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Four sprints from 17 August. The first is the platform; the last is testing and sign-off, which cannot share a sprint with development work at any team size.</t>
+          <t>Four blocks of work from 31 August. The first is the platform; the last is testing and sign-off, which cannot share a sprint with development work at any team size.</t>
         </is>
       </c>
     </row>
@@ -5634,31 +5674,31 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August)</t>
+          <t>Sprint 1 (31 August – 29 September)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mon 17 – Fri 28 Aug</t>
+          <t>Mon 31 Aug – Tue 29 Sep</t>
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>102 % ⚠</t>
+          <t>99 %</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -5670,31 +5710,31 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Sprint 2 (31 August – 11 September)</t>
+          <t>Sprint 2 (30 September – 20 October)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Mon 31 Aug – Fri 11 Sep</t>
+          <t>Wed 30 Sep – Tue 20 Oct</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>280</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>97 %</t>
+          <t>96 %</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -5706,52 +5746,52 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September)</t>
+          <t>Sprint 3 (21 October – 3 November)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mon 14 – Fri 18 Sep</t>
+          <t>Wed 21 Oct – Tue 3 Nov</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>89 %</t>
+          <t>94 %</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>6 close · 7 · spool completion · 8</t>
+          <t>6 close · 7 · spool completion · 8 · run-end write-back</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Sprint 4 (21–30 September)</t>
+          <t>Sprint 4 (4–16 November)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Mon 21 – Wed 30 Sep</t>
+          <t>Wed 4 Nov – Mon 16 Nov</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
@@ -5759,7 +5799,7 @@
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>0</v>
@@ -5814,66 +5854,66 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>5 → 4 developers (§2.1)</t>
+          <t>3 resources (the baseline — §2.1)</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Fri 18 Sep</t>
+          <t>Tue 3 Nov</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Wed 30 Sep</t>
+          <t>~Mon 16 Nov</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Meets the client's date with 42 h of slack, none of it in Sprint 1 — see §2.1's three ways out. Requires two additional people for Sprint 1 and one for Sprint 2–Sprint 3</t>
+          <t>869 h ÷ 19.5 h/day = 44.6 working days from 31 Aug, 46 once each block rounds. This is the staffed plan, not an option: it is what the team actually is</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>4 developers throughout</t>
+          <t>4 resources</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>~24–26 Sep</t>
+          <t>~Fri 16 Oct</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>~6–8 Oct</t>
+          <t>~late Oct</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>64 h short of closing on paper (768 h against 832). Viable only if both reserves are dropped and Sprint 1 starts early — it no longer closes on a single lever</t>
+          <t>26.0 h/day → 34 working days. Buys back roughly two and a half weeks. The fourth pair of hands is worth most in Sprint 1, where the three tracks genuinely parallelise</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>3 developers (current baseline)</t>
+          <t>5 resources</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>~6 Oct</t>
+          <t>~Wed 7 Oct</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>~mid Oct</t>
+          <t>~mid-Oct</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>832 h ÷ 24 h/day = 34.7 working days from 17 Aug. Development overruns 30 Sep; User Acceptance Testing then has nowhere to go. Lands inside the planned Q4 2026 production window</t>
+          <t>32.5 h/day → 27 working days. Beyond Sprint 1 the chain is sequential, so the fifth resource returns much less than the fourth — see §3</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5994,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -5974,7 +6014,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Sprint 1 (17–28 August) — 409 hours</t>
+          <t>Sprint 1 (31 August – 29 September) — 406 hours</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6041,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Days</t>
+          <t>Days (6.5 h)</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6065,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
@@ -6048,7 +6088,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
@@ -6071,7 +6111,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -6094,7 +6134,7 @@
         <v>75</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="10">
@@ -6117,7 +6157,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
@@ -6140,7 +6180,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -6155,7 +6195,7 @@
         <v>139</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>17.4</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="13">
@@ -6178,7 +6218,7 @@
         <v>14</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -6201,7 +6241,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="15">
@@ -6224,7 +6264,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="16">
@@ -6247,7 +6287,7 @@
         <v>14</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -6270,7 +6310,7 @@
         <v>16</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -6293,7 +6333,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
@@ -6316,7 +6356,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6379,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="21">
@@ -6362,7 +6402,7 @@
         <v>5</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22">
@@ -6385,7 +6425,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="23">
@@ -6408,7 +6448,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
@@ -6431,7 +6471,7 @@
         <v>21</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -6454,7 +6494,7 @@
         <v>5</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
@@ -6477,7 +6517,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="27">
@@ -6492,7 +6532,7 @@
         <v>145</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>18.1</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="28">
@@ -6515,7 +6555,7 @@
         <v>22</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="29">
@@ -6538,7 +6578,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="30">
@@ -6561,7 +6601,7 @@
         <v>7</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="31">
@@ -6584,7 +6624,7 @@
         <v>5</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="32">
@@ -6607,7 +6647,7 @@
         <v>11</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="33">
@@ -6622,7 +6662,7 @@
         <v>60</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -6633,19 +6673,19 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>FW-002</t>
+          <t>FW-004</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Being-flattened material status</t>
+          <t>Alloy reference data</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="35">
@@ -6656,19 +6696,19 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>FW-004</t>
+          <t>FW-005</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Alloy reference data</t>
+          <t>Equipment reference data</t>
         </is>
       </c>
       <c r="D35" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="36">
@@ -6679,16 +6719,16 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>FW-005</t>
+          <t>FW-006</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Equipment reference data</t>
+          <t>Material records</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>1.2</v>
@@ -6702,19 +6742,19 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>FW-006</t>
+          <t>FW-007</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Material records</t>
+          <t>Run and quality records</t>
         </is>
       </c>
       <c r="D37" s="8" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="38">
@@ -6725,950 +6765,950 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>FW-007</t>
+          <t>FW-152</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Run and quality records</t>
+          <t>Database build and rebuild</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Database (SQL Server)</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>FW-152</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Database build and rebuild</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>1</v>
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Database (SQL Server) — subtotal</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr"/>
+      <c r="C39" s="9" t="inlineStr"/>
+      <c r="D39" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Database (SQL Server) — subtotal</t>
+          <t>Sprint 1 (31 August – 29 September) — total</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr"/>
       <c r="C40" s="9" t="inlineStr"/>
       <c r="D40" s="10" t="n">
-        <v>65</v>
+        <v>406</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 1 (17–28 August) — total</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr"/>
-      <c r="C41" s="9" t="inlineStr"/>
-      <c r="D41" s="10" t="n">
-        <v>409</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>51.1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Sprint 2 (31 August – 11 September) — 280 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 2 (30 September – 20 October) — 280 hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Work item</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Days</t>
-        </is>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Days (6.5 h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Backend foundation close-out</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>FW-150</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Live reading delivery</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Backend foundation close-out</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>FW-150</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Live reading delivery</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="n">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>FW-151</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Machine settings service, with simulation</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="E45" s="7" t="n">
-        <v>1.4</v>
+      <c r="E45" s="8" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Backend foundation close-out</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>FW-151</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Machine settings service, with simulation</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="n">
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>FW-203</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Simulated machine data feed</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Backend foundation close-out</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>FW-205</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Run-block interlock</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Backend foundation close-out</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>FW-218</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Controls for the simulated machine data feed</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="E46" s="8" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Backend foundation close-out</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>FW-203</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Simulated machine data feed</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="n">
+      <c r="E48" s="7" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Backend foundation close-out — subtotal</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr"/>
+      <c r="C49" s="9" t="inlineStr"/>
+      <c r="D49" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>FW-153</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Connection loss handling</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>FW-155</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Fast active-run lookup</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>navigation</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>FW-204</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Line picker entry screen</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>navigation — subtotal</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr"/>
+      <c r="D53" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>FW-061</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Rod check-in screen</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>FW-082</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Machine configuration on check-in</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>FW-157</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Rod check-in transaction</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>FW-159</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Check-in write sequence</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>4 — subtotal</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr"/>
+      <c r="C58" s="9" t="inlineStr"/>
+      <c r="D58" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>FW-062</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Active run monitor</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>FW-081</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Live quality trace chart</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>FW-162</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Run status cards</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>FW-163</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Order and material detail panels</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>FW-164</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Run lookup and history</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>FW-165</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Fast quality history retrieval</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>FW-214</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Engineering console for the simulated machine</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>5 — subtotal</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr"/>
+      <c r="C66" s="9" t="inlineStr"/>
+      <c r="D66" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>6 (start)</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>FW-065</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Quality checkpoint capture</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>6 (start)</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>FW-071</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Pause and resume capture</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>6 (start)</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>FW-168</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Quality checkpoint transaction</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>6 (start)</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>FW-170</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Pause and resume transaction</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>6 (start)</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>FW-171</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>In-run event records</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="E47" s="7" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Backend foundation close-out</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>FW-205</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Run-block interlock</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>Backend foundation close-out</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>FW-218</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Controls for the simulated machine data feed</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>Backend foundation close-out — subtotal</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr"/>
-      <c r="C50" s="9" t="inlineStr"/>
-      <c r="D50" s="10" t="n">
-        <v>53</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>FW-153</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Connection loss handling</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E51" s="7" t="n">
+      <c r="E71" s="8" t="n">
         <v>0.9</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>FW-155</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Fast active-run lookup</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>navigation</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>FW-204</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Line picker entry screen</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E53" s="7" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>navigation — subtotal</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="inlineStr"/>
-      <c r="C54" s="9" t="inlineStr"/>
-      <c r="D54" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>FW-061</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Rod check-in screen</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="E55" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>FW-082</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Machine configuration on check-in</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>FW-157</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Rod check-in transaction</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="E57" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>FW-159</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Check-in write sequence</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr">
-        <is>
-          <t>4 — subtotal</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr"/>
-      <c r="C59" s="9" t="inlineStr"/>
-      <c r="D59" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>FW-062</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Active run monitor</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>FW-081</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Live quality trace chart</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="E61" s="7" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>FW-162</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Run status cards</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>FW-163</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Order and material detail panels</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="E63" s="7" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>FW-164</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Run lookup and history</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>FW-165</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Fast quality history retrieval</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E65" s="7" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>FW-214</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Engineering console for the simulated machine</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>5 — subtotal</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="inlineStr"/>
-      <c r="C67" s="9" t="inlineStr"/>
-      <c r="D67" s="10" t="n">
-        <v>89</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>6 (start)</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>FW-065</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Quality checkpoint capture</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>6 (start)</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>FW-071</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Pause and resume capture</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="E69" s="7" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>6 (start)</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>FW-168</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Quality checkpoint transaction</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>6 (start)</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>FW-170</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Pause and resume transaction</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E71" s="7" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>6 (start)</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>FW-171</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>In-run event records</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>0.8</v>
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>6 (start) — subtotal</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr"/>
+      <c r="C72" s="9" t="inlineStr"/>
+      <c r="D72" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>6 (start) — subtotal</t>
+          <t>Sprint 2 (30 September – 20 October) — total</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr"/>
       <c r="C73" s="9" t="inlineStr"/>
       <c r="D73" s="10" t="n">
-        <v>49</v>
+        <v>280</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 2 (31 August – 11 September) — total</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="inlineStr"/>
-      <c r="C74" s="9" t="inlineStr"/>
-      <c r="D74" s="10" t="n">
-        <v>280</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>Sprint 3 (14–18 September) — 143 hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 3 (21 October – 3 November) — 183 hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Work item</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>Days</t>
-        </is>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Days (6.5 h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>6 close</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>FW-172</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Events marked on the quality trace</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>6 close</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>FW-172</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Events marked on the quality trace</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="n">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>6 close — subtotal</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr"/>
+      <c r="C78" s="9" t="inlineStr"/>
+      <c r="D78" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="E78" s="7" t="n">
-        <v>0.9</v>
+      <c r="E78" s="10" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
-        <is>
-          <t>6 close — subtotal</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="inlineStr"/>
-      <c r="C79" s="9" t="inlineStr"/>
-      <c r="D79" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.9</v>
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>FW-067</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Material rejection capture</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>FW-067</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Material rejection capture</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="E80" s="7" t="n">
-        <v>1.6</v>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>FW-174</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Rejection transaction</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>FW-174</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Rejection transaction</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>1</v>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>FW-176</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Rejection records</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>FW-176</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Rejection records</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="n">
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>FW-177</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Supervisor notification</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E82" s="7" t="n">
-        <v>0.6</v>
+      <c r="E82" s="8" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>FW-177</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>Supervisor notification</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>0.6</v>
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>7 — subtotal</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr"/>
+      <c r="C83" s="9" t="inlineStr"/>
+      <c r="D83" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>7 — subtotal</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="inlineStr"/>
-      <c r="C84" s="9" t="inlineStr"/>
-      <c r="D84" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>3.9</v>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>FW-202</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Spool completion and weighing</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>10.3</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>FW-202</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>Spool completion and weighing</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>8.4</v>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>FW-219</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Finished coil recorded plant-wide</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>6.2</v>
       </c>
     </row>
     <row r="86">
@@ -7680,125 +7720,125 @@
       <c r="B86" s="10" t="inlineStr"/>
       <c r="C86" s="9" t="inlineStr"/>
       <c r="D86" s="10" t="n">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>FW-064</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>Spool check-in screen</t>
         </is>
       </c>
-      <c r="D87" s="8" t="n">
+      <c r="D87" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="E87" s="8" t="n">
+      <c r="E87" s="7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>FW-178</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Run monitor for the finishing line</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>FW-179</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Spool check-in transaction</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>FW-180</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Spool check-in records</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E90" s="8" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>FW-178</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>Run monitor for the finishing line</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E88" s="7" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>FW-179</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>Spool check-in transaction</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>FW-180</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>Spool check-in records</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E90" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>FW-181</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>Honest live reading on the finishing line</t>
         </is>
       </c>
-      <c r="D91" s="8" t="n">
+      <c r="D91" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E91" s="8" t="n">
-        <v>0.4</v>
+      <c r="E91" s="7" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="92">
@@ -7813,22 +7853,22 @@
         <v>38</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>Sprint 3 (14–18 September) — total</t>
+          <t>Sprint 3 (21 October – 3 November) — total</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr"/>
       <c r="C93" s="9" t="inlineStr"/>
       <c r="D93" s="10" t="n">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>17.9</v>
+        <v>28.2</v>
       </c>
     </row>
   </sheetData>
@@ -7843,7 +7883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7972,27 +8012,72 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Operator roles not confirmed</t>
+          <r>
+            <t xml:space="preserve">✅ </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Largely answered 15 Aug 2026</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> — the six roles already exist as sign-in permissions, so none need creating. </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>One detail is still outstanding.</t>
+          </r>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Confirmation that the operator, supervisor and operations manager roles already exist as sign-in permissions, or a decision to create them.</t>
+          <t>The exact codes used for the six roles. They are recorded in an abbreviated or coded form rather than as the role names we use in the permissions matrix, and we need the two lists lined up — which code corresponds to operator, supervisor, operations manager, engineering/maintenance, quality and administrator.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Every role-gated action in the trial</t>
+          <t>~~Every role-gated action in the trial~~ → the Sprint 1 QA0 walkthrough only</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Before Sprint 1 closes (28 Aug)</t>
+          <t>~~Before Sprint 1 closes (28 Aug)~~ → before the Sprint 1 QA0 walkthrough</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Every supervisor override and approval in the trial is blocked, including the weight-variance override on spool completion.</t>
+          <r>
+            <t xml:space="preserve">The supervisor overrides and approvals can be </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>built</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, but cannot be </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>checked</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> before the trial. A mismatched code does not raise an error — it silently denies a legitimate supervisor, or in the case of the supervisor notification, sends it to nobody.</t>
+          </r>
         </is>
       </c>
     </row>
@@ -8028,42 +8113,98 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Three plant-record values await confirmation</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Three values that a finished flat wire coil must carry in the existing plant records, each a question about systems that already exist rather than a design choice. First, the transaction name a flat wire coil completion should carry in the shop-floor history, and whether any current report or process filters on that name. Second, whether a finished flat wire coil should carry the existing on-skid status or needs one of its own. Third, what sample number and planned operations it should carry when they cannot be inherited from the rod. We have proposed an answer to each and each is a single-line change if the answer differs.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>FW-219 running anywhere but DEV; the §8 acceptance run if it is executed against a shared database</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Before the trial deploys outside DEV — ask now, it is a short conversation</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">The work can be </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>built and tested against development copies</t>
+          </r>
+          <r>
+            <t xml:space="preserve">, but </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>must not run against live plant data</t>
+          </r>
+          <r>
+            <t>. Getting one of these wrong does not raise an error — it writes a value an existing report may quietly filter out, and the impact review that would have identified which reports care was removed along with the shared-schema migration.</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Second tier — none of these stops the build</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>What we need</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Consequence if late</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Nine open questions with agreed workarounds</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Answers in due course on the footage-to-weight basis, which identifier the spool check-in scans, how a spool produced on the hybrid line is treated at the finishing line, what happens when no schedule matches, which order field carries the coil weight range, how a short close is transacted, and the live-data performance targets.</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>None immediately. Each has an agreed assumption the trial builds against, and a pass is scheduled in the final sprint to replace those assumptions once answers arrive.</t>
         </is>
@@ -8086,7 +8227,7 @@
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="128" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -8117,7 +8258,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Days</t>
+          <t>Days (6.5 h)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -8136,7 +8277,7 @@
         <v>42</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -8154,7 +8295,7 @@
         <v>70</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -8165,14 +8306,14 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>FW-001 shared-schema renames</t>
+          <t>FW-001 shared-schema renames — CANCELLED outright, D-32, 18 Aug 2026; no longer a descope decision</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
         <v>36</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -8190,7 +8331,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -8208,7 +8349,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -8226,7 +8367,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -8244,7 +8385,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -8262,7 +8403,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
@@ -8280,7 +8421,7 @@
         <v>39</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
@@ -8298,7 +8439,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -8316,7 +8457,7 @@
         <v>330</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>41.2</v>
+        <v>50.8</v>
       </c>
       <c r="D15" s="9" t="inlineStr"/>
     </row>
